--- a/docs/assessment/templates/vendor-third-party-risk-manager-checklist.xlsx
+++ b/docs/assessment/templates/vendor-third-party-risk-manager-checklist.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Extensibility Readiness (Graph Connectors, Plugins, Declarative Agents)</t>
+          <t>Extensibility Readiness (Copilot Connectors, Plugins, Declarative Agents)</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
